--- a/translations/welsh-translations.xlsx
+++ b/translations/welsh-translations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="501">
   <si>
     <t>Translator notes</t>
   </si>
@@ -37,6 +37,111 @@
     <t>Figma link</t>
   </si>
   <si>
+    <t>errorPages.400.pageTitle</t>
+  </si>
+  <si>
+    <t>errorPages.400</t>
+  </si>
+  <si>
+    <t>Bad Request</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>errorPages.401.pageTitle</t>
+  </si>
+  <si>
+    <t>errorPages.401</t>
+  </si>
+  <si>
+    <t>Unauthorized</t>
+  </si>
+  <si>
+    <t>errorPages.403.pageTitle</t>
+  </si>
+  <si>
+    <t>errorPages.403</t>
+  </si>
+  <si>
+    <t>Forbidden</t>
+  </si>
+  <si>
+    <t>errorPages.404.pageTitle</t>
+  </si>
+  <si>
+    <t>errorPages.404</t>
+  </si>
+  <si>
+    <t>Page not found</t>
+  </si>
+  <si>
+    <t>errorPages.404.heading</t>
+  </si>
+  <si>
+    <t>errorPages.404.body1</t>
+  </si>
+  <si>
+    <t>If you typed the web address, check it is correct.</t>
+  </si>
+  <si>
+    <t>errorPages.404.body2.prefix</t>
+  </si>
+  <si>
+    <t>errorPages.404.body2</t>
+  </si>
+  <si>
+    <t>You can also return to your account</t>
+  </si>
+  <si>
+    <t>errorPages.404.body2.linkText</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>errorPages.500.pageTitle</t>
+  </si>
+  <si>
+    <t>errorPages.500</t>
+  </si>
+  <si>
+    <t>Sorry, there is a technical problem</t>
+  </si>
+  <si>
+    <t>errorPages.500.heading</t>
+  </si>
+  <si>
+    <t>errorPages.500.body1</t>
+  </si>
+  <si>
+    <t>We can't access your information at the moment.</t>
+  </si>
+  <si>
+    <t>errorPages.500.body2</t>
+  </si>
+  <si>
+    <t>Try again later.</t>
+  </si>
+  <si>
+    <t>errorPages.500.body3.prefix</t>
+  </si>
+  <si>
+    <t>errorPages.500.body3</t>
+  </si>
+  <si>
+    <t>errorPages.500.body3.linkText</t>
+  </si>
+  <si>
+    <t>errorPages.default.pageTitle</t>
+  </si>
+  <si>
+    <t>errorPages.default</t>
+  </si>
+  <si>
+    <t>Something went wrong</t>
+  </si>
+  <si>
     <t>auth.signInFailed.heading</t>
   </si>
   <si>
@@ -49,9 +154,6 @@
     <t>Methu mewngofnodi</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>auth.signInFailed.noCredentials</t>
   </si>
   <si>
@@ -97,763 +199,1321 @@
     <t>You have signed out of the obligations service.</t>
   </si>
   <si>
-    <t>compliance.certificate.pageTitle</t>
+    <t>common.serviceName</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
+    <t>Report packaging data</t>
+  </si>
+  <si>
+    <t>common.warningIconFallback</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>common.regulation43Text</t>
+  </si>
+  <si>
+    <t>regulation 43</t>
+  </si>
+  <si>
+    <t>common.continue</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>common.opensInNewTab</t>
+  </si>
+  <si>
+    <t>opens in new tab</t>
+  </si>
+  <si>
+    <t>common.errorSummary.title</t>
+  </si>
+  <si>
+    <t>common.errorSummary</t>
+  </si>
+  <si>
+    <t>There is a problem</t>
+  </si>
+  <si>
+    <t>common.nav.home</t>
+  </si>
+  <si>
+    <t>common.nav</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>common.nav.back</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>common.nav.menu</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>common.nav.menuLabel</t>
+  </si>
+  <si>
+    <t>Show or hide menu</t>
+  </si>
+  <si>
+    <t>common.nav.manageAccount</t>
+  </si>
+  <si>
+    <t>Manage account</t>
+  </si>
+  <si>
+    <t>common.nav.signIn</t>
+  </si>
+  <si>
+    <t>Sign in</t>
+  </si>
+  <si>
+    <t>common.nav.signOut</t>
+  </si>
+  <si>
+    <t>Sign out</t>
+  </si>
+  <si>
+    <t>common.phaseBanner.tag</t>
+  </si>
+  <si>
+    <t>common.phaseBanner</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>common.phaseBanner.label</t>
+  </si>
+  <si>
+    <t>Beta banner</t>
+  </si>
+  <si>
+    <t>common.phaseBanner.lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a new service - your </t>
+  </si>
+  <si>
+    <t>common.phaseBanner.feedbackLink</t>
+  </si>
+  <si>
+    <t>feedback</t>
+  </si>
+  <si>
+    <t>common.phaseBanner.leadAfterLink</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> will help us to improve it.</t>
+  </si>
+  <si>
+    <t>common.languageSwitcher.label</t>
+  </si>
+  <si>
+    <t>common.languageSwitcher</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>common.languageSwitcher.english</t>
+  </si>
+  <si>
+    <t>common.languageSwitcher.welsh</t>
+  </si>
+  <si>
+    <t>Cymraeg</t>
+  </si>
+  <si>
+    <t>common.footer.getHelp</t>
+  </si>
+  <si>
+    <t>common.footer</t>
+  </si>
+  <si>
+    <t>Get help</t>
+  </si>
+  <si>
+    <t>common.footer.email</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>common.footer.telephone</t>
+  </si>
+  <si>
+    <t>Telephone</t>
+  </si>
+  <si>
+    <t>common.footer.openingTime</t>
+  </si>
+  <si>
+    <t>Monday to Friday, 8am to 6pm</t>
+  </si>
+  <si>
+    <t>common.footer.supportLinks</t>
+  </si>
+  <si>
+    <t>Support links</t>
+  </si>
+  <si>
+    <t>common.footer.cookies</t>
+  </si>
+  <si>
+    <t>Cookies</t>
+  </si>
+  <si>
+    <t>common.footer.privacy</t>
+  </si>
+  <si>
+    <t>Privacy</t>
+  </si>
+  <si>
+    <t>common.footer.accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility statement</t>
+  </si>
+  <si>
+    <t>common.footer.allContent</t>
+  </si>
+  <si>
+    <t>All content is available under the</t>
+  </si>
+  <si>
+    <t>common.footer.openGovernmentLicence</t>
+  </si>
+  <si>
+    <t>Open Government Licence v3.0</t>
+  </si>
+  <si>
+    <t>common.footer.exceptWhere</t>
+  </si>
+  <si>
+    <t>, except where otherwise stated</t>
+  </si>
+  <si>
+    <t>common.footer.crownCopyright</t>
+  </si>
+  <si>
+    <t>© Crown copyright</t>
+  </si>
+  <si>
+    <t>home.pageTitle</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>home.heading</t>
+  </si>
+  <si>
+    <t>about.pageTitle</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>about.heading</t>
+  </si>
+  <si>
+    <t>compliance.certificate.heading</t>
   </si>
   <si>
     <t>compliance.certificate</t>
   </si>
   <si>
-    <t>About your certificate of compliance</t>
-  </si>
-  <si>
-    <t>compliance.certificate.heading</t>
-  </si>
-  <si>
-    <t>compliance.certificate.description1</t>
-  </si>
-  <si>
-    <t>Your certificate of compliance tells the environmental regulator whether you have met your recycling obligations for {{year}}.</t>
-  </si>
-  <si>
-    <t>compliance.certificate.description2</t>
-  </si>
-  <si>
-    <t>You must submit a certificate of compliance whether or not you have met your recycling obligations.</t>
-  </si>
-  <si>
-    <t>compliance.certificate.description3</t>
-  </si>
-  <si>
-    <t>You must submit your certificate to the regulator before or on 31 January every year.</t>
-  </si>
-  <si>
-    <t>compliance.certificate.warning</t>
-  </si>
-  <si>
-    <t>You may be subject to enforcement action if you do not submit your certificate of compliance on time.</t>
-  </si>
-  <si>
-    <t>compliance.certificate.howToTitle</t>
+    <t>About your {{year}} certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.certificateSubmit.pageTitle</t>
+  </si>
+  <si>
+    <t>compliance.certificateSubmit</t>
+  </si>
+  <si>
+    <t>Check and submit your certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.certificateSubmit.heading</t>
+  </si>
+  <si>
+    <t>Check and submit your {{year}} certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statement.heading</t>
+  </si>
+  <si>
+    <t>compliance.statement</t>
+  </si>
+  <si>
+    <t>About your {{year}} statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.description1</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about</t>
+  </si>
+  <si>
+    <t>Your statement of compliance tells the {{regulatorName}} whether you have complied with regulation 43 in {{year}}.</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.mustBullet1</t>
+  </si>
+  <si>
+    <t>be an approved or delegated person to submit the statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.mustBullet2</t>
+  </si>
+  <si>
+    <t>submit the statement even if you have not complied with regulation 43</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.howToTitle</t>
+  </si>
+  <si>
+    <t>How to submit your statement</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.howToDescription</t>
+  </si>
+  <si>
+    <t>On the next screen you can check and submit your {{year}} statement of compliance.</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.regulatorContact</t>
+  </si>
+  <si>
+    <t>If anything on your statement is incorrect, contact the {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.statement.components.about.alreadySubmittedLead</t>
+  </si>
+  <si>
+    <t>You have already submitted your statement of compliance for {{year}}.</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.pageTitle</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit</t>
+  </si>
+  <si>
+    <t>Check and submit your statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.heading</t>
+  </si>
+  <si>
+    <t>Check and submit your {{year}} statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulatorInset.insetLead</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulatorInset</t>
+  </si>
+  <si>
+    <t>If anything on this page is incorrect, contact the {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.obligationsTable.tonnesNote</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.obligationsTable</t>
+  </si>
+  <si>
+    <t>All values are shown in tonnes.</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.declaration.intro</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.declaration</t>
+  </si>
+  <si>
+    <t>By entering your name and submitting this statement of compliance, you are verifying:</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.declaration.bullet1</t>
+  </si>
+  <si>
+    <t>you are an approved or delegated person who is eligible to submit this statement of compliance on behalf of {{complianceSchemeName}}</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.declaration.fullNameLabel</t>
+  </si>
+  <si>
+    <t>Enter your full name</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulation43.heading</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulation43</t>
+  </si>
+  <si>
+    <t>Regulation 43</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulation43.legendPrefix</t>
+  </si>
+  <si>
+    <t>In addition to the recycling obligations above, have you complied with all other requirements in</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulation43.legendSuffix</t>
+  </si>
+  <si>
+    <t>of the Producer Responsibility Obligations (Packaging and Packaging Waste) Regulations 2024?</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulation43.yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>compliance.statementSubmit.components.regulation43.no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.pageTitle</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess</t>
+  </si>
+  <si>
+    <t>Statement of compliance submitted</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.panelTitle</t>
+  </si>
+  <si>
+    <t>You have submitted your {{year}} statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.components.success.confirmationEmail</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.components.success</t>
+  </si>
+  <si>
+    <t>We have sent a confirmation email to: {{userEmail}}</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.components.success.publicRegisterBullet2</t>
+  </si>
+  <si>
+    <t>submitted your statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.components.success.regulatorBullet2</t>
+  </si>
+  <si>
+    <t>resubmit your statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.components.success.resubmitLead</t>
+  </si>
+  <si>
+    <t>If you need to resubmit your statement of compliance, contact the {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.heading</t>
+  </si>
+  <si>
+    <t>compliance.certificateView</t>
+  </si>
+  <si>
+    <t>{{year}} certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.overallStatus.overallMet</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.overallStatus</t>
+  </si>
+  <si>
+    <t>Recycling obligations met</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.overallStatus.overallNotMet</t>
+  </si>
+  <si>
+    <t>Recycling obligations not met</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.obligationsTable.obligationStatus.met</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.obligationsTable.obligationStatus</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.obligationsTable.obligationStatus.notMet</t>
+  </si>
+  <si>
+    <t>Not met</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.obligationsTable.obligationStatus.noDataYet</t>
+  </si>
+  <si>
+    <t>No data yet</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.page.preHeader</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.page</t>
+  </si>
+  <si>
+    <t>Producer Responsibility Obligations (Packaging and Packaging Waste) Regulations 2024</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.page.verifiedByPrefix</t>
+  </si>
+  <si>
+    <t>Certificate verified by:</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.page.returnButton</t>
+  </si>
+  <si>
+    <t>Return to your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.certificateView.components.page.downloadLink</t>
+  </si>
+  <si>
+    <t>Download or print</t>
+  </si>
+  <si>
+    <t>compliance.statementView.heading</t>
+  </si>
+  <si>
+    <t>compliance.statementView</t>
+  </si>
+  <si>
+    <t>{{year}} statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.heading</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus</t>
+  </si>
+  <si>
+    <t>Compliance status</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.obligationsMetCompliedStrapline</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.notCompliantReg43Strapline</t>
+  </si>
+  <si>
+    <t>Not compliant with regulation 43 requirements</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.obligationsMetCompliedSubtext</t>
+  </si>
+  <si>
+    <t>{{complianceSchemeName}} met its {{year}} recycling obligations and complied with all other regulation 43 requirements.</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.obligationsMetReg43NotCompliedSubtext</t>
+  </si>
+  <si>
+    <t>{{complianceSchemeName}} met its {{year}} recycling obligations but did not comply with all other regulation 43 requirements.</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.obligationsNotMetReg43CompliedSubtext</t>
+  </si>
+  <si>
+    <t>{{complianceSchemeName}} did not meet its {{year}} recycling obligations but did comply with all other regulation 43 requirements.</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.complianceStatus.obligationsNotMetReg43NotCompliedSubtext</t>
+  </si>
+  <si>
+    <t>{{complianceSchemeName}} did not meet its {{year}} recycling obligations or comply with all other regulation 43 requirements.</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.obligationsTable.tonnesNote</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.obligationsTable</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.obligationsTable.obligationStatus.met</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.obligationsTable.obligationStatus</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.obligationsTable.obligationStatus.notMet</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.obligationsTable.obligationStatus.noDataYet</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.page.preHeader</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.page</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.page.verifiedByPrefix</t>
+  </si>
+  <si>
+    <t>Statement verified by:</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.page.downloadPdfButton</t>
+  </si>
+  <si>
+    <t>Download as PDF</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.page.printButton</t>
+  </si>
+  <si>
+    <t>Print</t>
+  </si>
+  <si>
+    <t>compliance.statementView.components.page.returnButton</t>
+  </si>
+  <si>
+    <t>compliance.submitError.heading</t>
+  </si>
+  <si>
+    <t>compliance.submitError</t>
+  </si>
+  <si>
+    <t>Sorry, there has been a technical error</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.homepage.prefix</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.homepage</t>
+  </si>
+  <si>
+    <t>Return to your account</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.homepage.linkText</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.certificate.body1</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.certificate</t>
+  </si>
+  <si>
+    <t>Your certificate of compliance may not have been submitted.</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.certificate.body2</t>
+  </si>
+  <si>
+    <t>Check your email inbox for confirmation. If you have not received a confirmation email, you will need to submit your certificate again.</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.statement.body1</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.statement</t>
+  </si>
+  <si>
+    <t>Your statement of compliance may not have been submitted.</t>
+  </si>
+  <si>
+    <t>compliance.submitError.components.statement.body2</t>
+  </si>
+  <si>
+    <t>Check your email inbox for confirmation. If you have not received a confirmation email, you will need to submit your statement again.</t>
+  </si>
+  <si>
+    <t>compliance.certificateSuccess.pageTitle</t>
+  </si>
+  <si>
+    <t>compliance.certificateSuccess</t>
+  </si>
+  <si>
+    <t>Certificate of compliance submitted</t>
+  </si>
+  <si>
+    <t>compliance.certificateSuccess.panelTitle</t>
+  </si>
+  <si>
+    <t>You have submitted your {{year}} certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.certificateSuccess.components.success.confirmationEmail</t>
+  </si>
+  <si>
+    <t>compliance.certificateSuccess.components.success</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.heading</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList</t>
+  </si>
+  <si>
+    <t>Organisation details</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.organisationName</t>
+  </si>
+  <si>
+    <t>Organisation name</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.organisationId</t>
+  </si>
+  <si>
+    <t>Organisation ID</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.complianceScheme</t>
+  </si>
+  <si>
+    <t>Compliance scheme</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.schemeOperator</t>
+  </si>
+  <si>
+    <t>Compliance scheme operator</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.address</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.nameOnAccount</t>
+  </si>
+  <si>
+    <t>Name on account</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.regulator</t>
+  </si>
+  <si>
+    <t>Regulator</t>
+  </si>
+  <si>
+    <t>compliance.components.summaryList.submissionDate</t>
+  </si>
+  <si>
+    <t>Date of submission</t>
+  </si>
+  <si>
+    <t>compliance.components.regulatorInset.insetLead</t>
+  </si>
+  <si>
+    <t>compliance.components.regulatorInset</t>
+  </si>
+  <si>
+    <t>If any information on this page is incorrect, contact the {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.components.overallStatus.recyclingObligationsHeading</t>
+  </si>
+  <si>
+    <t>compliance.components.overallStatus</t>
+  </si>
+  <si>
+    <t>Recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.overallStatus.recyclingObligationsStatusHeading</t>
+  </si>
+  <si>
+    <t>Recycling obligations status</t>
+  </si>
+  <si>
+    <t>compliance.components.overallStatus.overallMet</t>
+  </si>
+  <si>
+    <t>Recycling obligations have been met</t>
+  </si>
+  <si>
+    <t>compliance.components.overallStatus.overallNotMet</t>
+  </si>
+  <si>
+    <t>Recycling obligations have not been met</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.recyclingObligationsHeading</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tonnesNote</t>
+  </si>
+  <si>
+    <t>All values are shown in whole tonnes.</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.glassHeading</t>
+  </si>
+  <si>
+    <t>Glass recycling obligation breakdown</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableMaterial</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableObligationToMeet</t>
+  </si>
+  <si>
+    <t>Recycling obligations to meet</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableAwaiting</t>
+  </si>
+  <si>
+    <t>Tonnage awaiting acceptance</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableAccepted</t>
+  </si>
+  <si>
+    <t>Tonnage accepted</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableOutstanding</t>
+  </si>
+  <si>
+    <t>Tonnage outstanding</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableStatus</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.paperComposite</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material</t>
+  </si>
+  <si>
+    <t>Paper, board or fibre-based composite material</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.plastic</t>
+  </si>
+  <si>
+    <t>Plastic</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.wood</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.steel</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.aluminium</t>
+  </si>
+  <si>
+    <t>Aluminium</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.glass</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.glassRemelt</t>
+  </si>
+  <si>
+    <t>Glass remelt</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.glassRemaining</t>
+  </si>
+  <si>
+    <t>Remaining glass</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.default</t>
+  </si>
+  <si>
+    <t>{{name}}</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.table.totalsRow</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.table</t>
+  </si>
+  <si>
+    <t>Totals</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.obligationStatus.met</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.obligationStatus</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.obligationStatus.notMet</t>
+  </si>
+  <si>
+    <t>NOT MET</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.obligationStatus.noDataYet</t>
+  </si>
+  <si>
+    <t>NO DATA YET</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.heading</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration</t>
+  </si>
+  <si>
+    <t>Declaration</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.intro</t>
+  </si>
+  <si>
+    <t>By entering your name and submitting this certificate of compliance, you are verifying:</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.bullet1</t>
+  </si>
+  <si>
+    <t>you are an approved or delegated person who is eligible to submit this certificate of compliance on behalf of {{organisationName}}</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.bullet2</t>
+  </si>
+  <si>
+    <t>the information you are submitting is accurate</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.bullet3</t>
+  </si>
+  <si>
+    <t>you understand that you may face enforcement action if you submit false or misleading information</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.fullNameLabel</t>
+  </si>
+  <si>
+    <t>Your full name</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.submitButton</t>
+  </si>
+  <si>
+    <t>Confirm and submit</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.cancelLink</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>compliance.components.success.whatHappensNext</t>
+  </si>
+  <si>
+    <t>compliance.components.success</t>
+  </si>
+  <si>
+    <t>What happens next</t>
+  </si>
+  <si>
+    <t>compliance.components.success.confirmationEmail</t>
+  </si>
+  <si>
+    <t>We have sent a confirmation email to the email addresses on your account.</t>
+  </si>
+  <si>
+    <t>compliance.components.success.certificateLinkLead</t>
+  </si>
+  <si>
+    <t>You will find a link to your certificate of compliance at the bottom of the</t>
+  </si>
+  <si>
+    <t>compliance.components.success.certificateLinkSuffix</t>
+  </si>
+  <si>
+    <t>page.</t>
+  </si>
+  <si>
+    <t>compliance.components.success.statementLinkLead</t>
+  </si>
+  <si>
+    <t>You will find a link to your statement of compliance at the bottom of the</t>
+  </si>
+  <si>
+    <t>compliance.components.success.statementLinkSuffix</t>
+  </si>
+  <si>
+    <t>compliance.components.success.manageObligationsLink</t>
+  </si>
+  <si>
+    <t>Manage your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.success.regulatorMayAsk</t>
+  </si>
+  <si>
+    <t>The {{regulatorName}} will contact you if they want you to:</t>
+  </si>
+  <si>
+    <t>compliance.components.success.regulatorBullet1</t>
+  </si>
+  <si>
+    <t>provide more information</t>
+  </si>
+  <si>
+    <t>compliance.components.success.regulatorBullet2</t>
+  </si>
+  <si>
+    <t>resubmit your certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterLead</t>
+  </si>
+  <si>
+    <t>They will also update</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterLink</t>
+  </si>
+  <si>
+    <t>the public register</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterSuffix</t>
+  </si>
+  <si>
+    <t>to show that you have:</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterBullet1Met</t>
+  </si>
+  <si>
+    <t>met your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterBullet1NotMet</t>
+  </si>
+  <si>
+    <t>not met your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterBullet2</t>
+  </si>
+  <si>
+    <t>submitted your certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterRegulation43Complied</t>
+  </si>
+  <si>
+    <t>complied with regulation 43 requirements</t>
+  </si>
+  <si>
+    <t>compliance.components.success.publicRegisterRegulation43NotComplied</t>
+  </si>
+  <si>
+    <t>not complied with regulation 43 requirements</t>
+  </si>
+  <si>
+    <t>compliance.components.success.resubmitLead</t>
+  </si>
+  <si>
+    <t>If you need to resubmit your certificate of compliance, contact the {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.components.success.returnLink</t>
+  </si>
+  <si>
+    <t>Return to recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.success.viewCertificateButton</t>
+  </si>
+  <si>
+    <t>View your certificate</t>
+  </si>
+  <si>
+    <t>compliance.components.success.viewStatementButton</t>
+  </si>
+  <si>
+    <t>View your statement</t>
+  </si>
+  <si>
+    <t>compliance.components.about.mustIntro</t>
+  </si>
+  <si>
+    <t>compliance.components.about</t>
+  </si>
+  <si>
+    <t>You must:</t>
+  </si>
+  <si>
+    <t>compliance.components.about.warning</t>
+  </si>
+  <si>
+    <t>You may face enforcement action if you miss the deadline.</t>
+  </si>
+  <si>
+    <t>compliance.components.about.description1</t>
+  </si>
+  <si>
+    <t>Your certificate of compliance tells the {{regulatorName}} whether you have met your recycling obligations for {{year}}.</t>
+  </si>
+  <si>
+    <t>compliance.components.about.introPrefix</t>
+  </si>
+  <si>
+    <t>Compliance schemes must comply with</t>
+  </si>
+  <si>
+    <t>compliance.components.about.introSuffix</t>
+  </si>
+  <si>
+    <t>of the Producer Responsibility Obligations (Packaging and Packaging Waste) Regulations 2024. This includes:</t>
+  </si>
+  <si>
+    <t>compliance.components.about.bullet1</t>
+  </si>
+  <si>
+    <t>registering compliance scheme members</t>
+  </si>
+  <si>
+    <t>compliance.components.about.bullet2</t>
+  </si>
+  <si>
+    <t>reporting members' packaging data</t>
+  </si>
+  <si>
+    <t>compliance.components.about.bullet3</t>
+  </si>
+  <si>
+    <t>meeting recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.about.mustBullet1</t>
+  </si>
+  <si>
+    <t>be an approved or delegated person to submit the certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.components.about.mustBullet2</t>
+  </si>
+  <si>
+    <t>submit the certificate even if you have not met your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.about.mustBullet3</t>
+  </si>
+  <si>
+    <t>submit on or before 31 January every year</t>
+  </si>
+  <si>
+    <t>compliance.components.about.howToTitle</t>
   </si>
   <si>
     <t>How to submit your certificate</t>
   </si>
   <si>
-    <t>compliance.certificate.howToDescription1</t>
-  </si>
-  <si>
-    <t>You must be an approved or delegated person to submit a certificate of compliance.</t>
-  </si>
-  <si>
-    <t>compliance.certificate.howToDescription2</t>
-  </si>
-  <si>
-    <t>On the next screen you will see a copy of your certificate for {{year}}. Before submitting it, you must:</t>
-  </si>
-  <si>
-    <t>compliance.certificate.bullet1</t>
-  </si>
-  <si>
-    <t>check that the details are correct</t>
-  </si>
-  <si>
-    <t>compliance.certificate.bullet2</t>
-  </si>
-  <si>
-    <t>provide your name</t>
-  </si>
-  <si>
-    <t>compliance.certificate.regulatorPrefix</t>
-  </si>
-  <si>
-    <t>If any details are incorrect, contact your environmental regulator:</t>
-  </si>
-  <si>
-    <t>compliance.certificate.downloadDescription</t>
-  </si>
-  <si>
-    <t>You will be able to download or print your certificate after submission.</t>
-  </si>
-  <si>
-    <t>compliance.certificate.alreadySubmittedLead</t>
+    <t>compliance.components.about.howToDescription</t>
+  </si>
+  <si>
+    <t>On the next screen you can check and submit your {{year}} certificate of compliance.</t>
+  </si>
+  <si>
+    <t>compliance.components.about.howToBeforeSubmitIntro</t>
+  </si>
+  <si>
+    <t>Before submitting, you must:</t>
+  </si>
+  <si>
+    <t>compliance.components.about.howToBullet1</t>
+  </si>
+  <si>
+    <t>check your organisation details</t>
+  </si>
+  <si>
+    <t>compliance.components.about.howToBullet2</t>
+  </si>
+  <si>
+    <t>check your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.about.howToBullet3</t>
+  </si>
+  <si>
+    <t>confirm whether you've complied with all other regulation 43 requirements</t>
+  </si>
+  <si>
+    <t>compliance.components.about.howToBulletFullName</t>
+  </si>
+  <si>
+    <t>enter your full name underneath the legal declaration</t>
+  </si>
+  <si>
+    <t>compliance.components.about.regulatorContact</t>
+  </si>
+  <si>
+    <t>If anything on your certificate is incorrect, contact the {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.components.about.finalStatus</t>
+  </si>
+  <si>
+    <t>Your final certificate shows your recycling obligations status. To get a 'met' status, you must have met all of your recycling obligations.</t>
+  </si>
+  <si>
+    <t>compliance.components.about.finalStatusIntro</t>
+  </si>
+  <si>
+    <t>Your final statement will show your compliance status. To be compliant, you must have:</t>
+  </si>
+  <si>
+    <t>compliance.components.about.finalStatusBullet1</t>
+  </si>
+  <si>
+    <t>compliance.components.about.finalStatusBullet2</t>
+  </si>
+  <si>
+    <t>complied with all other regulation 43 requirements</t>
+  </si>
+  <si>
+    <t>compliance.components.about.alreadySubmittedLead</t>
   </si>
   <si>
     <t>You have already submitted your certificate of compliance for {{year}}.</t>
   </si>
   <si>
-    <t>compliance.certificate.viewSubmissionButton</t>
+    <t>compliance.components.about.viewSubmissionButton</t>
   </si>
   <si>
     <t>View confirmation</t>
   </si>
   <si>
-    <t>compliance.certificateSubmit.pageTitle</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit</t>
-  </si>
-  <si>
-    <t>Check and submit your certificate of compliance</t>
-  </si>
-  <si>
-    <t>https://www.figma.com/design/eG3Z7k6gmh9ZCtooRy0iBz/Certificate-Statement-of-Certification?node-id=4297-32941&amp;t=Q3O1BsyGQFlPiGHY-0</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.heading</t>
-  </si>
-  <si>
-    <t>Check and submit your {{year}} certificate of compliance</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.insetLead</t>
-  </si>
-  <si>
-    <t>If any information on this page is incorrect, contact the {{regulatorName}}:</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.summaryOrganisationName</t>
-  </si>
-  <si>
-    <t>Organisation name</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.summaryOrganisationId</t>
-  </si>
-  <si>
-    <t>Organisation ID</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.summaryAddress</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.summaryNameOnAccount</t>
-  </si>
-  <si>
-    <t>Name on account</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.summaryRegulator</t>
-  </si>
-  <si>
-    <t>Regulator</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.overallMet</t>
-  </si>
-  <si>
-    <t>Recycling obligations have been met</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.overallNotMet</t>
-  </si>
-  <si>
-    <t>Recycling obligations have not been met</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tonnesNote</t>
-  </si>
-  <si>
-    <t>All values are shown in whole tonnes.</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tableMaterial</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tableObligationToMeet</t>
-  </si>
-  <si>
-    <t>Recycling obligations to meet</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tableAwaiting</t>
-  </si>
-  <si>
-    <t>Tonnage awaiting acceptance</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tableAccepted</t>
-  </si>
-  <si>
-    <t>Tonnage accepted</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tableOutstanding</t>
-  </si>
-  <si>
-    <t>Tonnage outstanding</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.tableStatus</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.glassHeading</t>
-  </si>
-  <si>
-    <t>Glass recycling obligation breakdown</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.declarationHeading</t>
-  </si>
-  <si>
-    <t>Declaration</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.declarationIntro</t>
-  </si>
-  <si>
-    <t>By entering your name and submitting this certificate of compliance, you are verifying:</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.declarationBullet1</t>
-  </si>
-  <si>
-    <t>you are an approved or delegated person who is eligible to submit this certificate of compliance on behalf of {{organisationName}}</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.declarationBullet2</t>
-  </si>
-  <si>
-    <t>the information you are submitting is accurate</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.declarationBullet3</t>
-  </si>
-  <si>
-    <t>you understand that you may face enforcement action if you submit false or misleading information</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.fullNameLabel</t>
-  </si>
-  <si>
-    <t>Your full name</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.fullNameHint</t>
-  </si>
-  <si>
-    <t>Enter your full name as it appears on this account</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.submitButton</t>
-  </si>
-  <si>
-    <t>Confirm and submit</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.cancelLink</t>
-  </si>
-  <si>
-    <t>Cancel</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.paperComposite</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material</t>
-  </si>
-  <si>
-    <t>Paper, board or fibre-based composite material</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.plastic</t>
-  </si>
-  <si>
-    <t>Plastic</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.wood</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.steel</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.aluminium</t>
-  </si>
-  <si>
-    <t>Aluminium</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.glass</t>
-  </si>
-  <si>
-    <t>Glass</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.glassRemelt</t>
-  </si>
-  <si>
-    <t>Glass remelt</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.glassRemaining</t>
-  </si>
-  <si>
-    <t>Remaining glass</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.material.default</t>
-  </si>
-  <si>
-    <t>{{name}}</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.table.totalsRow</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.table</t>
-  </si>
-  <si>
-    <t>Totals</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.obligationStatus.met</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.obligationStatus</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.obligationStatus.notMet</t>
-  </si>
-  <si>
-    <t>NOT MET</t>
-  </si>
-  <si>
-    <t>compliance.certificateSubmit.obligationStatus.noDataYet</t>
-  </si>
-  <si>
-    <t>NO DATA YET</t>
-  </si>
-  <si>
-    <t>compliance.statement.pageTitle</t>
-  </si>
-  <si>
-    <t>compliance.statement</t>
-  </si>
-  <si>
-    <t>About your statement of compliance</t>
-  </si>
-  <si>
-    <t>compliance.statement.heading</t>
-  </si>
-  <si>
-    <t>compliance.statement.description1Prefix</t>
-  </si>
-  <si>
-    <t>Your statement of compliance tells the environmental regulator whether, in the past year, you have met the requirements in</t>
-  </si>
-  <si>
-    <t>compliance.statement.description1Suffix</t>
-  </si>
-  <si>
-    <t>of the Producer Responsibility Regulations (Packaging and Packaging Waste) Regulations 2024.</t>
-  </si>
-  <si>
-    <t>compliance.statement.includes</t>
-  </si>
-  <si>
-    <t>This includes:</t>
-  </si>
-  <si>
-    <t>compliance.statement.bullet1</t>
-  </si>
-  <si>
-    <t>registering producers who are members of your compliance scheme</t>
-  </si>
-  <si>
-    <t>compliance.statement.bullet2</t>
-  </si>
-  <si>
-    <t>reporting their packaging data</t>
-  </si>
-  <si>
-    <t>compliance.statement.bullet3</t>
-  </si>
-  <si>
-    <t>meeting your recycling obligations</t>
-  </si>
-  <si>
-    <t>compliance.statement.description2</t>
-  </si>
-  <si>
-    <t>You must submit a statement of compliance whether or not you have complied with the requirements of regulation 43.</t>
-  </si>
-  <si>
-    <t>compliance.statement.description3</t>
-  </si>
-  <si>
-    <t>You must submit the statement to the environmental regulator before or on 31 January every year.</t>
-  </si>
-  <si>
-    <t>compliance.statement.warning</t>
-  </si>
-  <si>
-    <t>You may be subject to enforcement action if you do not submit your statement of compliance on time.</t>
-  </si>
-  <si>
-    <t>compliance.statement.howToTitle</t>
-  </si>
-  <si>
-    <t>How to submit your statement</t>
-  </si>
-  <si>
-    <t>compliance.statement.howToDescription1</t>
-  </si>
-  <si>
-    <t>You must be an approved or delegated person to submit the statement of compliance.</t>
-  </si>
-  <si>
-    <t>compliance.statement.howToDescription2</t>
-  </si>
-  <si>
-    <t>On the next screen, you will see a copy of your statement for {{year}}. Before submitting it, you must:</t>
-  </si>
-  <si>
-    <t>compliance.statement.howToBullet1</t>
-  </si>
-  <si>
-    <t>check the details are correct</t>
-  </si>
-  <si>
-    <t>compliance.statement.howToBullet2</t>
-  </si>
-  <si>
-    <t>compliance.statement.regulatorPrefix</t>
-  </si>
-  <si>
-    <t>compliance.statement.downloadDescription</t>
-  </si>
-  <si>
-    <t>You will be able to download or print your statement after submission.</t>
-  </si>
-  <si>
-    <t>compliance.statement.continueUnavailableHint</t>
-  </si>
-  <si>
-    <t>Continuing to submit your statement is not available yet.</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.pageTitle</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess</t>
-  </si>
-  <si>
-    <t>Certificate of compliance submitted</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.panelTitle</t>
-  </si>
-  <si>
-    <t>You have submitted your {{year}} certificate of compliance</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.whatHappensNext</t>
-  </si>
-  <si>
-    <t>What happens next</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.statusSubmitted</t>
-  </si>
-  <si>
-    <t>You submitted your certificate of compliance with a ‘{{status}}’ status.</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.confirmationEmail</t>
-  </si>
-  <si>
-    <t>We have sent a confirmation email to everybody registered on your account.</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.regulatorMayAsk</t>
-  </si>
-  <si>
-    <t>The {{regulatorName}} will contact you if they want you to:</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.regulatorBullet1</t>
-  </si>
-  <si>
-    <t>provide more information</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.regulatorBullet2</t>
-  </si>
-  <si>
-    <t>resubmit your certificate of compliance</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.publicRegisterLead</t>
-  </si>
-  <si>
-    <t>They will also update</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.publicRegisterLink</t>
-  </si>
-  <si>
-    <t>the public register</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.publicRegisterSuffix</t>
-  </si>
-  <si>
-    <t>to show that you have met your recycling obligations and submitted your certificate.</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.resubmitLead</t>
-  </si>
-  <si>
-    <t>If you need to resubmit your certificate of compliance, contact the {{regulatorName}}:</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.viewCertificateButton</t>
-  </si>
-  <si>
-    <t>View your certificate</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.viewCertificateHint</t>
-  </si>
-  <si>
-    <t>Viewing your certificate is not available yet.</t>
-  </si>
-  <si>
-    <t>compliance.certificateSuccess.returnLink</t>
-  </si>
-  <si>
-    <t>Return to recycling obligations</t>
-  </si>
-  <si>
-    <t>compliance.common.warningIconFallback</t>
-  </si>
-  <si>
-    <t>compliance.common</t>
-  </si>
-  <si>
-    <t>Warning</t>
-  </si>
-  <si>
-    <t>compliance.common.regulation43Text</t>
-  </si>
-  <si>
-    <t>regulation 43</t>
-  </si>
-  <si>
-    <t>compliance.common.continue</t>
-  </si>
-  <si>
-    <t>Continue</t>
-  </si>
-  <si>
-    <t>compliance.common.opensInNewTab</t>
-  </si>
-  <si>
-    <t>opens in new tab</t>
-  </si>
-  <si>
-    <t>compliance.common.nav.home</t>
-  </si>
-  <si>
-    <t>compliance.common.nav</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>compliance.common.nav.menu</t>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>compliance.common.nav.menuLabel</t>
-  </si>
-  <si>
-    <t>Show or hide menu</t>
-  </si>
-  <si>
-    <t>compliance.common.nav.manageAccount</t>
-  </si>
-  <si>
-    <t>Manage account</t>
-  </si>
-  <si>
-    <t>compliance.common.nav.signOut</t>
-  </si>
-  <si>
-    <t>Sign out</t>
-  </si>
-  <si>
-    <t>compliance.common.phaseBanner.tag</t>
-  </si>
-  <si>
-    <t>compliance.common.phaseBanner</t>
-  </si>
-  <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>compliance.common.phaseBanner.lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a new service - your </t>
-  </si>
-  <si>
-    <t>compliance.common.phaseBanner.feedbackLink</t>
-  </si>
-  <si>
-    <t>feedback</t>
-  </si>
-  <si>
-    <t>compliance.common.phaseBanner.leadAfterLink</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> will help us to improve it.</t>
-  </si>
-  <si>
-    <t>compliance.common.languageSwitcher.label</t>
-  </si>
-  <si>
-    <t>compliance.common.languageSwitcher</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>compliance.common.languageSwitcher.english</t>
-  </si>
-  <si>
-    <t>compliance.common.languageSwitcher.welsh</t>
-  </si>
-  <si>
-    <t>Cymraeg</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.getHelp</t>
-  </si>
-  <si>
-    <t>compliance.common.footer</t>
-  </si>
-  <si>
-    <t>Get help</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.email</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.telephone</t>
-  </si>
-  <si>
-    <t>Telephone</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.openingTime</t>
-  </si>
-  <si>
-    <t>Monday to Friday, 8am to 6pm</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.supportLinks</t>
-  </si>
-  <si>
-    <t>Support links</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.cookies</t>
-  </si>
-  <si>
-    <t>Cookies</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.privacy</t>
-  </si>
-  <si>
-    <t>Privacy</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.accessibility</t>
-  </si>
-  <si>
-    <t>Accessibility statement</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.allContent</t>
-  </si>
-  <si>
-    <t>All content is available under the</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.openGovernmentLicence</t>
-  </si>
-  <si>
-    <t>Open Government Licence v3.0</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.exceptWhere</t>
-  </si>
-  <si>
-    <t>, except where otherwise stated</t>
-  </si>
-  <si>
-    <t>compliance.common.footer.crownCopyright</t>
-  </si>
-  <si>
-    <t>© Crown copyright</t>
-  </si>
-  <si>
-    <t>compliance.accessibility.organisationDetailsHeading</t>
-  </si>
-  <si>
-    <t>compliance.accessibility</t>
-  </si>
-  <si>
-    <t>Organisation details</t>
-  </si>
-  <si>
-    <t>compliance.accessibility.overallStatusHeading</t>
-  </si>
-  <si>
-    <t>Overall recycling obligation status</t>
-  </si>
-  <si>
-    <t>compliance.accessibility.obligationsTableCaption</t>
-  </si>
-  <si>
-    <t>Recycling obligations by material, in tonnes</t>
-  </si>
-  <si>
-    <t>compliance.accessibility.glassTableCaption</t>
-  </si>
-  <si>
-    <t>Glass recycling obligations, in tonnes</t>
+    <t>compliance.errors.submitDeclaration</t>
+  </si>
+  <si>
+    <t>compliance.errors</t>
+  </si>
+  <si>
+    <t>Unable to submit compliance declaration</t>
+  </si>
+  <si>
+    <t>compliance.errors.prepareCertificate</t>
+  </si>
+  <si>
+    <t>Unable to prepare certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.errors.prepareStatement</t>
+  </si>
+  <si>
+    <t>Unable to prepare statement of compliance</t>
+  </si>
+  <si>
+    <t>compliance.errors.missingSubmitCache</t>
+  </si>
+  <si>
+    <t>Unable to find submit cache payload for {{year}} year</t>
+  </si>
+  <si>
+    <t>compliance.validation.fullName.empty</t>
+  </si>
+  <si>
+    <t>compliance.validation.fullName</t>
+  </si>
+  <si>
+    <t>You must enter your full name</t>
+  </si>
+  <si>
+    <t>compliance.validation.fullName.tooShort</t>
+  </si>
+  <si>
+    <t>Your name must be more than one character</t>
+  </si>
+  <si>
+    <t>compliance.validation.fullName.tooLong</t>
+  </si>
+  <si>
+    <t>Your name must be fewer than 255 characters</t>
+  </si>
+  <si>
+    <t>compliance.validation.fullName.invalidChars</t>
+  </si>
+  <si>
+    <t>Your name cannot contain these characters: @, #, $, %, &amp;, &lt;, &gt;</t>
+  </si>
+  <si>
+    <t>compliance.validation.regulation43.empty</t>
+  </si>
+  <si>
+    <t>compliance.validation.regulation43</t>
+  </si>
+  <si>
+    <t>You must select 'yes' or 'no' to continue</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -1312,27 +1972,27 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1340,2579 +2000,4519 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C45" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>5</v>
+        <v>259</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3921,9 +6521,6 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="F29" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
